--- a/data/extracted_100_brand_new_100k_500k_batch6.xlsx
+++ b/data/extracted_100_brand_new_100k_500k_batch6.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q37"/>
+  <dimension ref="A1:Q101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3370,6 +3370,5062 @@
         </is>
       </c>
     </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>rosefittt</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Kimberly Miller</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>rosefittt@gmail.com</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>217K</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
+        <v>217100</v>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Travel</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Miami, FL, US</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Bodybuilding and CrossFit Athlete: Lifestyle, Travel, and Rave</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/rosefittt</t>
+        </is>
+      </c>
+      <c r="K38" t="b">
+        <v>1</v>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>$100</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>1 Instagram Story</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>https://hoo.be/rosefittt</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>not_sent</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>2026-09-18T13:12:03.413474+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>marcel</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Marcel Williams</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>hi@marcel.plus</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>188K</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
+        <v>187600</v>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA, US</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Entertainment and Lifestyle Creator</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/marcel</t>
+        </is>
+      </c>
+      <c r="K39" t="b">
+        <v>1</v>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>$1,000</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>1 Instagram Photo Feed Post</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>https://solo.to/marcel</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>not_sent</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>2026-09-18T13:10:45.86601+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>alainatsang</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Alaina Tsang</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>alainatsang123@gmail.com</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>125K</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
+        <v>124600</v>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Vegan</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Miami Beach, FL, US</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Lifestyle digital creator</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/alainatsang</t>
+        </is>
+      </c>
+      <c r="K40" t="b">
+        <v>1</v>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>$500</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>1 TikTok Story</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>https://linktr.ee/alainatsang</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>not_sent</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>2026-09-18T13:10:11.80539+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>nayle</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Nayle Aleman</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>zenidinovanajle@gmail.com</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>197K</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
+        <v>197400</v>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Comedy &amp; Entertainment</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Kissimmee, FL, US</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Dynamic Video Creator Specializing in Engaging Content</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nayle</t>
+        </is>
+      </c>
+      <c r="K41" t="b">
+        <v>1</v>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>$55</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>1 Instagram Story</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>https://taplink.cc/nayle</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>not_sent</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>2026-09-18T13:09:39.651037+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>vibewithmolly</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Mommy.Inc</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>vibewithmollys@gmail.com</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>100K</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
+        <v>100000</v>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Comedy &amp; Entertainment</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA, US</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>“Mom Vibe Curator | Real Talk, Humor &amp; Everyday Wins</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/vibewithmolly</t>
+        </is>
+      </c>
+      <c r="K42" t="b">
+        <v>1</v>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>$250</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>4.8</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>1 Instagram Reel</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>https://msha.ke/vibewithmolly</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>not_sent</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>2026-09-18T13:09:23.755207+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>justinalmeida</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Justin Almeida</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>justinalmeidamgmt@gmail.com</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>192K</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
+        <v>192300</v>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Athlete &amp; Sports</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Orlando, FL, US</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Student Athlete | Content Creator | Lifestyle</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/justinalmeida</t>
+        </is>
+      </c>
+      <c r="K43" t="b">
+        <v>1</v>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>$50</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>4.6</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>1 TikTok Story</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>https://linktr.ee/justinalmeida</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>not_sent</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>2026-09-18T13:08:50.12975+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>hunterreynolds</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Hunter Reynolds</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>hunterreynoldsactor@gmail.com</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>141K</t>
+        </is>
+      </c>
+      <c r="F44" t="n">
+        <v>140900</v>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Athlete &amp; Sports</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>South Orange, NJ, US</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Sports Content Creator &amp; Athlete</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/hunterreynolds</t>
+        </is>
+      </c>
+      <c r="K44" t="b">
+        <v>1</v>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>$1,250</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>1 Instagram Story</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>https://linktr.ee/hunterreynolds</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>not_sent</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>2026-09-18T13:08:48.645481+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>pailynnpashelle</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Pailynn Moore</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>info@pailynnpashelle.com</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>101K</t>
+        </is>
+      </c>
+      <c r="F45" t="n">
+        <v>100800</v>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Entrepreneur &amp; Business</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Social Media Influencer | Content Creator</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/pailynnpashelle</t>
+        </is>
+      </c>
+      <c r="K45" t="b">
+        <v>1</v>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>$50</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>1 TikTok Story</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>https://beacons.ai/pailynnpashelle</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>not_sent</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>2026-09-18T13:08:08.036497+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>azhaiboggs</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Azhai Boggs</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>azhaiboggsbusiness@gmail.com</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>429K</t>
+        </is>
+      </c>
+      <c r="F46" t="n">
+        <v>429300</v>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Austin, TX, US</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Fashion, Tech, Lifestyle Creator</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/azhaiboggs</t>
+        </is>
+      </c>
+      <c r="K46" t="b">
+        <v>1</v>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>$1,000</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>1 Instagram Reel</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>https://stan.store/azhaiboggs</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>not_sent</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>2026-09-18T13:07:31.162707+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>megivarshanidze</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Megivarshanidze</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>megivarshanidze2017@gmail.com</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>107K</t>
+        </is>
+      </c>
+      <c r="F47" t="n">
+        <v>106800</v>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>DIY &amp; Craft</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Wilmington, DE, US</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>fashion skincare beauty</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/megivarshanidze</t>
+        </is>
+      </c>
+      <c r="K47" t="b">
+        <v>1</v>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>$200</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>1 Instagram Story</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>https://linktr.ee/megivarshanidze</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>not_sent</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>2026-09-18T13:07:25.338631+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>danfabervocalstudio</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Dan Faber</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>danfabervocalstudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>136K</t>
+        </is>
+      </c>
+      <c r="F48" t="n">
+        <v>136400</v>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Actor</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>New York, NY, US</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Voice Teacher &amp; Vocal Coach</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/danfabervocalstudio</t>
+        </is>
+      </c>
+      <c r="K48" t="b">
+        <v>1</v>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>$650</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>5 TikTok Videos</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>https://linktr.ee/danfabervocalstudio</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>not_sent</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>2026-09-18T13:07:23.140513+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>briaspen</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Bri Aspen</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>brianagabemusic@gmail.com</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>140K</t>
+        </is>
+      </c>
+      <c r="F49" t="n">
+        <v>140300</v>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Music &amp; Dance</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Nashville, TN, US</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Musician, Micro-influencer, and Livestream</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/briaspen</t>
+        </is>
+      </c>
+      <c r="K49" t="b">
+        <v>1</v>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>$50</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>1 TikTok Story</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>https://linktr.ee/briaspen</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>not_sent</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>2026-09-18T13:07:22.917617+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>krystalhall</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Krystal Hall</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>southernnsalty@gmail.com</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>174K</t>
+        </is>
+      </c>
+      <c r="F50" t="n">
+        <v>173700</v>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Outdoor &amp; Nature</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Sarasota, FL, US</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Adventure and Outdoor Creator</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/krystalhall</t>
+        </is>
+      </c>
+      <c r="K50" t="b">
+        <v>1</v>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>$300</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>1 TikTok Video</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>https://direct.me/krystalhall</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>not_sent</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>2026-09-18T13:06:53.932392+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>kwabbie</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Kwabbie Oppong</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>kwabbiek@gmail.com</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>122K</t>
+        </is>
+      </c>
+      <c r="F51" t="n">
+        <v>122200</v>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Actor</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA, US</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Cultural content creator and actor</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/kwabbie</t>
+        </is>
+      </c>
+      <c r="K51" t="b">
+        <v>1</v>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>$750</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>1 Instagram Reel</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>https://linktr.ee/kwabbie</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>not_sent</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>2026-09-18T13:06:53.501014+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>araboffgrid</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Arab Off Grid</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>araboffgrid@gmail.com</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>402K</t>
+        </is>
+      </c>
+      <c r="F52" t="n">
+        <v>402400</v>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Chattanooga, TN, US</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Off Grid living, Building a house, sustainable living</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/araboffgrid</t>
+        </is>
+      </c>
+      <c r="K52" t="b">
+        <v>1</v>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>$200</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>1 Instagram Story</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>https://linktr.ee/araboffgrid</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>not_sent</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>2026-09-18T13:06:41.415996+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>gokceercann</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Gokce Ercan</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>gokce@gaiabreeze.com</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>341K</t>
+        </is>
+      </c>
+      <c r="F53" t="n">
+        <v>340600</v>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Tampa, FL, US</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Content Creator</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/gokceercann</t>
+        </is>
+      </c>
+      <c r="K53" t="b">
+        <v>1</v>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>$500</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>3 Instagram Photo Feed Posts</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>https://linktr.ee/gokceercann</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>not_sent</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>2026-09-18T13:06:41.110212+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>livwillson</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Olivia Grace Willson</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>contactoliviawillson@gmail.com</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>105K</t>
+        </is>
+      </c>
+      <c r="F54" t="n">
+        <v>105200</v>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Influencer, content creator, model, actress</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/livwillson</t>
+        </is>
+      </c>
+      <c r="K54" t="b">
+        <v>1</v>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>$1,000</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>3.8</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>1 Instagram Reel (2 Minutes)</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>https://hoo.be/livwillson</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>not_sent</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>2026-09-18T13:05:59.965719+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>joshsadowski</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Josh Sadowski</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>business@joshsadowski.com</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>290K</t>
+        </is>
+      </c>
+      <c r="F55" t="n">
+        <v>289700</v>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Comedy &amp; Entertainment</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA, US</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>content creator and musician</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/joshsadowski</t>
+        </is>
+      </c>
+      <c r="K55" t="b">
+        <v>1</v>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>$150</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>1 Instagram Story</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>https://linktr.ee/joshsadowski</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>not_sent</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>2026-09-18T13:05:57.846338+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>khalietheflowergirl</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Khalie Watkins</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>khalie@noceurmedia.com</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>406K</t>
+        </is>
+      </c>
+      <c r="F56" t="n">
+        <v>405900</v>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Comedy &amp; Entertainment</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Memphis, TN, US</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Home-makeover enthusiast and lifestyle influencer</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/khalietheflowergirl</t>
+        </is>
+      </c>
+      <c r="K56" t="b">
+        <v>1</v>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>$100</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>1 TikTok Story</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>https://linktr.ee/khalietheflowergirl</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>not_sent</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>2026-09-18T13:05:57.634158+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>atsunamatsui</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Atsuna Matsui</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>contact@atsunamatsui.com</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>362K</t>
+        </is>
+      </c>
+      <c r="F57" t="n">
+        <v>361800</v>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA, US</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Lifestyle Content Creator</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/atsunamatsui</t>
+        </is>
+      </c>
+      <c r="K57" t="b">
+        <v>1</v>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>$589</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>1 Instagram Story</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>https://hoo.be/atsunamatsui</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>not_sent</t>
+        </is>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>2026-09-18T13:05:31.067568+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>hertimelesslife</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Her Timeless Life</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>hertimelesslife@gmail.com</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>154K</t>
+        </is>
+      </c>
+      <c r="F58" t="n">
+        <v>153800</v>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Vegan</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Knoxville, TN, US</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>Vintage and Elegant Fashion Influencer</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/hertimelesslife</t>
+        </is>
+      </c>
+      <c r="K58" t="b">
+        <v>1</v>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>$1,200</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>2 Instagram Reels (20 Seconds)</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>https://stan.store/hertimelesslife</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>not_sent</t>
+        </is>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>2026-09-18T13:05:29.924637+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>rushfighter</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Rushfighter</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>rushfighter00@gmail.com</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>109K</t>
+        </is>
+      </c>
+      <c r="F59" t="n">
+        <v>109000</v>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Comedy &amp; Entertainment</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>New York, NY, US</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>🎥 Comedy | POV | Lifestyle</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/rushfighter</t>
+        </is>
+      </c>
+      <c r="K59" t="b">
+        <v>1</v>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>$200</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>1 Instagram Reel (60 Seconds)</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>https://linktr.ee/rushfighter</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>not_sent</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>2026-09-18T13:05:28.928219+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>terryberry</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Theresa</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>theresa@aceinfluencers.com</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>327K</t>
+        </is>
+      </c>
+      <c r="F60" t="n">
+        <v>327300</v>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Denver, CO, US</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>Fashion Content Creator</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/terryberry</t>
+        </is>
+      </c>
+      <c r="K60" t="b">
+        <v>1</v>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>$350</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>1 Instagram Story</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>https://linktr.ee/terryberry</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>not_sent</t>
+        </is>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>2026-09-18T13:05:28.713259+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>oodhamboi</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Wagon Burner</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>oodhamboiii@gmail.com</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>410K</t>
+        </is>
+      </c>
+      <c r="F61" t="n">
+        <v>409800</v>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Education</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>San Jose, CA, US</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>Education &amp; Advocacy Content Creator</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/oodhamboi</t>
+        </is>
+      </c>
+      <c r="K61" t="b">
+        <v>1</v>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>$200</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>1 TikTok Story</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>https://linktr.ee/oodhamboi</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>not_sent</t>
+        </is>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>2026-09-18T13:05:28.509679+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>madisonamateau</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Madison Amateau</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>contact.madisonamateau@gmail.com</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>111K</t>
+        </is>
+      </c>
+      <c r="F62" t="n">
+        <v>111100</v>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA, US</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>Social Media Influencer</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/madisonamateau</t>
+        </is>
+      </c>
+      <c r="K62" t="b">
+        <v>1</v>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>$1,500</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>1 Instagram Photo Feed Post</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>https://linktr.ee/madisonamateau</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>not_sent</t>
+        </is>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>2026-09-18T13:05:28.305496+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>brookenix</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Brookenix12</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>info@brookenix.com</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>108K</t>
+        </is>
+      </c>
+      <c r="F63" t="n">
+        <v>107900</v>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Athlete &amp; Sports</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Boynton Beach, FL, US</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>Hi! 👋🏻 I’m Brooke Nix! Focused on lifestyle, family, humor and more!</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/brookenix</t>
+        </is>
+      </c>
+      <c r="K63" t="b">
+        <v>1</v>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>$250</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>1 Instagram Photo Feed Post</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>https://linktr.ee/brookenix</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>not_sent</t>
+        </is>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>2026-09-18T13:05:00.018761+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>spreadtheword</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Justin Douglas</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>stwcreative@gmail.com</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>164K</t>
+        </is>
+      </c>
+      <c r="F64" t="n">
+        <v>164400</v>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Outdoor &amp; Nature</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Tampa, FL, US</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>Fitness Content Creator</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/spreadtheword</t>
+        </is>
+      </c>
+      <c r="K64" t="b">
+        <v>1</v>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>$199</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>1 Instagram Reel</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>https://msha.ke/spreadtheword</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>not_sent</t>
+        </is>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>2026-09-18T13:04:56.068309+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>rhymecology</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Jeff Walker</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>rhymecology@gmail.com</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr"/>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>203K</t>
+        </is>
+      </c>
+      <c r="F65" t="n">
+        <v>203100</v>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Education</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA, US</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>Music and Education Creator</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/rhymecology</t>
+        </is>
+      </c>
+      <c r="K65" t="b">
+        <v>1</v>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>$115</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>1 Instagram Story</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>https://linktr.ee/rhymecology</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>not_sent</t>
+        </is>
+      </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>2026-09-18T13:04:50.306723+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>msmaverickmuse</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Morgan Ryan</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>msmaverickmuse@gmail.com</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>298K</t>
+        </is>
+      </c>
+      <c r="F66" t="n">
+        <v>298500</v>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Schenectady, NY, US</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>Style + Glam Content Creator</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/msmaverickmuse</t>
+        </is>
+      </c>
+      <c r="K66" t="b">
+        <v>1</v>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>$2,000</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>1 Instagram Reel</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>https://linktr.ee/msmaverickmuse</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>not_sent</t>
+        </is>
+      </c>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>2026-09-18T13:04:49.366197+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>thecre8ivechick</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Ilonka Margis</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>thecre8ivechick@yahoo.com</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>139K</t>
+        </is>
+      </c>
+      <c r="F67" t="n">
+        <v>139200</v>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Animals &amp; Pets</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Austin, TX, US</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>Horse &amp; dog content creator</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/thecre8ivechick</t>
+        </is>
+      </c>
+      <c r="K67" t="b">
+        <v>1</v>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>$500</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>1 TikTok Video</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>https://linktr.ee/thecre8ivechick</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>not_sent</t>
+        </is>
+      </c>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>2026-09-18T13:04:22.127086+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>kaylaazjones</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Kayla Jones</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>jaylee@notalent.com</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>343K</t>
+        </is>
+      </c>
+      <c r="F68" t="n">
+        <v>343000</v>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Athlete &amp; Sports</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>West Palm Beach, FL, US</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>Lifestyle and golf content creator</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/kaylaazjones</t>
+        </is>
+      </c>
+      <c r="K68" t="b">
+        <v>1</v>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>$100</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>1 TikTok Story</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>https://hoo.be/kaylaazjones</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>not_sent</t>
+        </is>
+      </c>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t>2026-09-18T13:04:18.972912+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>theerinmarie</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Erin Marie Smelcer</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>theerinmarie15@gmail.com</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>174K</t>
+        </is>
+      </c>
+      <c r="F69" t="n">
+        <v>173600</v>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Madison, WI, US</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>Social Media Content Creator</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/theerinmarie</t>
+        </is>
+      </c>
+      <c r="K69" t="b">
+        <v>1</v>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>$300</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>1 TikTok Video (60 Seconds)</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>https://linktr.ee/theerinmarie</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>not_sent</t>
+        </is>
+      </c>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>2026-09-18T13:04:13.788642+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>joegranitto</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Joe Granitto</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>pr@joegranitto.com</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>134K</t>
+        </is>
+      </c>
+      <c r="F70" t="n">
+        <v>133800</v>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Hobart, IN, US</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>UGC Creator &amp; Photographer | Authentic Content + 144k Audience Reach</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/joegranitto</t>
+        </is>
+      </c>
+      <c r="K70" t="b">
+        <v>1</v>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>$50</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>1 Instagram Story</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>https://linktr.ee/joegranitto</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>not_sent</t>
+        </is>
+      </c>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>2026-09-18T13:04:12.211365+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>cozysquirrel</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Cozysquirrel</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>cozysquirrelyt@gmail.com</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr"/>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>123K</t>
+        </is>
+      </c>
+      <c r="F71" t="n">
+        <v>123200</v>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>Cozy Gaming &amp; Tech Content Creator</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/cozysquirrel</t>
+        </is>
+      </c>
+      <c r="K71" t="b">
+        <v>1</v>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>$149</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>1 Instagram Story</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>https://linktr.ee/cozysquirrel</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>not_sent</t>
+        </is>
+      </c>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t>2026-09-18T13:04:11.189322+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>mrsdeependa</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Anne Gabey</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>mrsdeependa@gmail.com</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr"/>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>272K</t>
+        </is>
+      </c>
+      <c r="F72" t="n">
+        <v>272100</v>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Food &amp; Drink</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>San Diego, CA, US</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>Food Content Creator, Recipe developer</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/mrsdeependa</t>
+        </is>
+      </c>
+      <c r="K72" t="b">
+        <v>1</v>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>$1,000</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>1 Instagram Reel</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>https://linktr.ee/mrsdeependa</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>not_sent</t>
+        </is>
+      </c>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>2026-09-18T13:04:10.774648+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>zoodraws</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Brian Ahearn</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>heyzoodraws@gmail.com</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr"/>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>111K</t>
+        </is>
+      </c>
+      <c r="F73" t="n">
+        <v>111200</v>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Outdoor &amp; Nature</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Oneonta, NY, US</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>Creative artist and engaging science communicator</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/zoodraws</t>
+        </is>
+      </c>
+      <c r="K73" t="b">
+        <v>1</v>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>$800</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>1 Instagram Photo Feed Post</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>https://linktr.ee/zoodraws</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>not_sent</t>
+        </is>
+      </c>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>2026-09-18T13:03:42.615096+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>momoneydoll</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Monique Loya</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>moneydolltoys@yahoo.com</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>134K</t>
+        </is>
+      </c>
+      <c r="F74" t="n">
+        <v>134400</v>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Art &amp; Photography</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA, US</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>art, fashion, entertainment</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/momoneydoll</t>
+        </is>
+      </c>
+      <c r="K74" t="b">
+        <v>1</v>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>$50</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>1 TikTok Story</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>https://linktr.ee/momoneydoll</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>not_sent</t>
+        </is>
+      </c>
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t>2026-09-18T13:03:40.476232+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>myaustinhaven</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Jennifer Valtierra</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>myaustinhaven@gmail.com</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr"/>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>332K</t>
+        </is>
+      </c>
+      <c r="F75" t="n">
+        <v>332300</v>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Home &amp; Garden</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Austin, TX, US</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>Home Decor Content Creator</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/myaustinhaven</t>
+        </is>
+      </c>
+      <c r="K75" t="b">
+        <v>1</v>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>$250</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>1 Instagram Story</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>https://msha.ke/myaustinhaven</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>not_sent</t>
+        </is>
+      </c>
+      <c r="Q75" t="inlineStr">
+        <is>
+          <t>2026-09-18T13:03:28.790171+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>nailsbydaovo</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Dao Vo</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>nailsbydaovo@gmail.com</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr"/>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>112K</t>
+        </is>
+      </c>
+      <c r="F76" t="n">
+        <v>111500</v>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA, US</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>Nail Content Creator</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nailsbydaovo</t>
+        </is>
+      </c>
+      <c r="K76" t="b">
+        <v>1</v>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>$100</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>1 Instagram Story</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>https://stan.store/nailsbydaovo</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>not_sent</t>
+        </is>
+      </c>
+      <c r="Q76" t="inlineStr">
+        <is>
+          <t>2026-09-18T13:02:22.402449+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>pacu</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Niko Lucky</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>fantasticpacu@gmail.com</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr"/>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>175K</t>
+        </is>
+      </c>
+      <c r="F77" t="n">
+        <v>174600</v>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Animals &amp; Pets</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Coeur d'Alene, ID, US</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>Animal Facts / Gaming Streamer</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/pacu</t>
+        </is>
+      </c>
+      <c r="K77" t="b">
+        <v>1</v>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>$100</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>1 TikTok Story</t>
+        </is>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>https://campsite.bio/pacu</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>not_sent</t>
+        </is>
+      </c>
+      <c r="Q77" t="inlineStr">
+        <is>
+          <t>2026-09-18T13:01:48.347363+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>jacindatravels</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Jacinda</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>jacindatravels@gmail.com</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr"/>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>132K</t>
+        </is>
+      </c>
+      <c r="F78" t="n">
+        <v>131900</v>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Music &amp; Dance</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>Wanderlust Photographer: Sharing Captivating Travel Adventures</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/jacindatravels</t>
+        </is>
+      </c>
+      <c r="K78" t="b">
+        <v>1</v>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>$75</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>1 Instagram Story</t>
+        </is>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>https://msha.ke/jacindatravels</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>not_sent</t>
+        </is>
+      </c>
+      <c r="Q78" t="inlineStr">
+        <is>
+          <t>2026-09-18T13:01:15.381467+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>youknowzach</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Zach Day</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>youknowzach@gmail.com</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr"/>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>104K</t>
+        </is>
+      </c>
+      <c r="F79" t="n">
+        <v>103600</v>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Music &amp; Dance</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Nashville, TN, US</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>A Touring Musician Sharing Lifestyle and Behind-the-Scenes Insights</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/youknowzach</t>
+        </is>
+      </c>
+      <c r="K79" t="b">
+        <v>1</v>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>$500</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>1 Instagram Story</t>
+        </is>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>https://msha.ke/youknowzach</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>not_sent</t>
+        </is>
+      </c>
+      <c r="Q79" t="inlineStr">
+        <is>
+          <t>2026-09-18T13:01:10.195938+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>pineappleprincesscreations</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Miranda Miele</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>pineappleprincesscreations@gmail.com</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr"/>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>265K</t>
+        </is>
+      </c>
+      <c r="F80" t="n">
+        <v>264900</v>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>DIY &amp; Craft</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>North Weymouth, MA, US</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>DIY Content Creator, Celebrity Sneaker and Heels Artist, Rhinestone Artist</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/pineappleprincesscreations</t>
+        </is>
+      </c>
+      <c r="K80" t="b">
+        <v>1</v>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>$200</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>1 Instagram Story</t>
+        </is>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>https://beacons.ai/pineappleprincesscreations</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>not_sent</t>
+        </is>
+      </c>
+      <c r="Q80" t="inlineStr">
+        <is>
+          <t>2026-09-18T13:01:04.525784+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>madisonlmills</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Madi Mills</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>madisonlmills01@gmail.com</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr"/>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>125K</t>
+        </is>
+      </c>
+      <c r="F81" t="n">
+        <v>124700</v>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Tampa, FL, US</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>Content creator and fashion model</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/madisonlmills</t>
+        </is>
+      </c>
+      <c r="K81" t="b">
+        <v>1</v>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>$225</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>1 Instagram Reel</t>
+        </is>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>https://beacons.ai/madisonlmills</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>not_sent</t>
+        </is>
+      </c>
+      <c r="Q81" t="inlineStr">
+        <is>
+          <t>2026-09-18T13:00:52.686526+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>rondo</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Kymani</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>francescopiolops+smm@gmail.com</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr"/>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>299K</t>
+        </is>
+      </c>
+      <c r="F82" t="n">
+        <v>299100</v>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Comedy &amp; Entertainment</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Cumming, GA, US</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>Hoop Entertainment Creator</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/rondo</t>
+        </is>
+      </c>
+      <c r="K82" t="b">
+        <v>1</v>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>$300</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>1 Instagram Story</t>
+        </is>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>https://taplink.cc/rondo</t>
+        </is>
+      </c>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>not_sent</t>
+        </is>
+      </c>
+      <c r="Q82" t="inlineStr">
+        <is>
+          <t>2026-09-18T12:59:45.747723+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>fentifriedchicken</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Fenti Fried Chicken</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>fentifriedchicken@gmail.com</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr"/>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>371K</t>
+        </is>
+      </c>
+      <c r="F83" t="n">
+        <v>370600</v>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Comedy &amp; Entertainment</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Boston, MA, US</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>Comedian - Finance, Boston, &amp; Skits</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/fentifriedchicken</t>
+        </is>
+      </c>
+      <c r="K83" t="b">
+        <v>1</v>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>$5,000</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>1 TikTok Video</t>
+        </is>
+      </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>https://hoo.be/fentifriedchicken</t>
+        </is>
+      </c>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>not_sent</t>
+        </is>
+      </c>
+      <c r="Q83" t="inlineStr">
+        <is>
+          <t>2026-09-18T12:59:41.118684+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>kingmoxu</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>King Moxu</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>moxu@sunandskyentertainment.com</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr"/>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>130K</t>
+        </is>
+      </c>
+      <c r="F84" t="n">
+        <v>129500</v>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Comedy &amp; Entertainment</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Fremont, OH, US</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>Comedy Content Creator</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/kingmoxu</t>
+        </is>
+      </c>
+      <c r="K84" t="b">
+        <v>1</v>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>$2,200</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>1 Instagram Story</t>
+        </is>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>https://direct.me/kingmoxu</t>
+        </is>
+      </c>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>not_sent</t>
+        </is>
+      </c>
+      <c r="Q84" t="inlineStr">
+        <is>
+          <t>2026-09-18T12:57:28.191756+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>victorburgos</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Victor Burgos</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>victorburgosrevilla@gmail.com</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr"/>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>153K</t>
+        </is>
+      </c>
+      <c r="F85" t="n">
+        <v>153200</v>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Celebrity &amp; Public Figure</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Houston, TX, US</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>Creador de contenido exitoso</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/victorburgos</t>
+        </is>
+      </c>
+      <c r="K85" t="b">
+        <v>1</v>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>$100</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>1 Instagram Story</t>
+        </is>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>https://taplink.cc/victorburgos</t>
+        </is>
+      </c>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>not_sent</t>
+        </is>
+      </c>
+      <c r="Q85" t="inlineStr">
+        <is>
+          <t>2026-09-18T12:56:49.404858+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>siberianderpskies</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Jonathan Brinksman</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>jonathan@siberianderpskies.com</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr"/>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>476K</t>
+        </is>
+      </c>
+      <c r="F86" t="n">
+        <v>475800</v>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Animals &amp; Pets</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>A pet and comedy content creator with an irreverent style and a heart of gold.</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/siberianderpskies</t>
+        </is>
+      </c>
+      <c r="K86" t="b">
+        <v>1</v>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>$450</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>1 Instagram Photo Feed Post</t>
+        </is>
+      </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>https://campsite.bio/siberianderpskies</t>
+        </is>
+      </c>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>not_sent</t>
+        </is>
+      </c>
+      <c r="Q86" t="inlineStr">
+        <is>
+          <t>2026-09-18T12:56:46.723714+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>okayjaclyn</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Jaclyn</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>okayjaclyn@gmail.com</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr"/>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>235K</t>
+        </is>
+      </c>
+      <c r="F87" t="n">
+        <v>235000</v>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Comedy &amp; Entertainment</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Portland, OR, US</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>Tiktok Content Creator</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/okayjaclyn</t>
+        </is>
+      </c>
+      <c r="K87" t="b">
+        <v>1</v>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>$500</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>1 TikTok Video (15 Seconds)</t>
+        </is>
+      </c>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>https://beacons.ai/okayjaclyn</t>
+        </is>
+      </c>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>not_sent</t>
+        </is>
+      </c>
+      <c r="Q87" t="inlineStr">
+        <is>
+          <t>2026-09-18T12:55:48.785073+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>epicluvv</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Melva Simpson</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>melandsimpson@gmail.com</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr"/>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>223K</t>
+        </is>
+      </c>
+      <c r="F88" t="n">
+        <v>222900</v>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Comedy &amp; Entertainment</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Detroit, MI, US</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>Lifestyle | Amazon Reviews | Product Unboxing Content Creator</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/epicluvv</t>
+        </is>
+      </c>
+      <c r="K88" t="b">
+        <v>1</v>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>$300</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>1 TikTok Video (30 Seconds)</t>
+        </is>
+      </c>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>https://hoo.be/epicluvv</t>
+        </is>
+      </c>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>not_sent</t>
+        </is>
+      </c>
+      <c r="Q88" t="inlineStr">
+        <is>
+          <t>2026-09-18T12:55:39.876059+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>lyssamfit</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Alyssa Perez</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>alyssamfit@gmail.com</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr"/>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>228K</t>
+        </is>
+      </c>
+      <c r="F89" t="n">
+        <v>227900</v>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Entrepreneur &amp; Business</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Lakewood, CA, US</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>Fitness content creator</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/lyssamfit</t>
+        </is>
+      </c>
+      <c r="K89" t="b">
+        <v>1</v>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>$50</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>1 TikTok Story</t>
+        </is>
+      </c>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>https://hoo.be/lyssamfit</t>
+        </is>
+      </c>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>not_sent</t>
+        </is>
+      </c>
+      <c r="Q89" t="inlineStr">
+        <is>
+          <t>2026-09-18T12:53:17.951462+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>foryousage</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Chad Kawalec</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>chadkawalec@gmail.com</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr"/>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>161K</t>
+        </is>
+      </c>
+      <c r="F90" t="n">
+        <v>161400</v>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Lifestyle</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>A Top Content Creator for Relationship, Self-Improvement &amp; Cat Advice</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/foryousage</t>
+        </is>
+      </c>
+      <c r="K90" t="b">
+        <v>1</v>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>$625</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>1 Instagram Reel</t>
+        </is>
+      </c>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>https://direct.me/foryousage</t>
+        </is>
+      </c>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>not_sent</t>
+        </is>
+      </c>
+      <c r="Q90" t="inlineStr">
+        <is>
+          <t>2026-09-18T12:52:37.048295+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>sierranielsen</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Sierra Nielsen</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>sierra@sierranielsen.com</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr"/>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>232K</t>
+        </is>
+      </c>
+      <c r="F91" t="n">
+        <v>231500</v>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Lifestyle</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA, US</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>Fitness, Health and Lifestyle Content Creator</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/sierranielsen</t>
+        </is>
+      </c>
+      <c r="K91" t="b">
+        <v>1</v>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>$1,500</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>1 Instagram Reel</t>
+        </is>
+      </c>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>https://hoo.be/sierranielsen</t>
+        </is>
+      </c>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>not_sent</t>
+        </is>
+      </c>
+      <c r="Q91" t="inlineStr">
+        <is>
+          <t>2026-09-18T12:51:21.451328+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>cassielee</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Promote with Cassie Lee</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>cassieerbe@gmail.com</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr"/>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>349K</t>
+        </is>
+      </c>
+      <c r="F92" t="n">
+        <v>349300</v>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Baltimore, MD, US</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>Model &amp; Influencer</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/cassielee</t>
+        </is>
+      </c>
+      <c r="K92" t="b">
+        <v>1</v>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>$200</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>1 Instagram Photo Feed Post</t>
+        </is>
+      </c>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>https://stan.store/cassielee</t>
+        </is>
+      </c>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>not_sent</t>
+        </is>
+      </c>
+      <c r="Q92" t="inlineStr">
+        <is>
+          <t>2026-09-18T12:48:04.341456+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>adrianjohnson</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Promote with Adrian Johnson</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>adrianjohnson707@aol.com</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr"/>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>130K</t>
+        </is>
+      </c>
+      <c r="F93" t="n">
+        <v>130000</v>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Athlete &amp; Sports</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Clifton Forge, VA, US</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>Professional cornhole player for the American cornhole league</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/adrianjohnson</t>
+        </is>
+      </c>
+      <c r="K93" t="b">
+        <v>1</v>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>$500</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>1 Instagram Story</t>
+        </is>
+      </c>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>https://hoo.be/adrianjohnson</t>
+        </is>
+      </c>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>not_sent</t>
+        </is>
+      </c>
+      <c r="Q93" t="inlineStr">
+        <is>
+          <t>2026-09-18T12:48:00.034689+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>kyleemroz</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Promote with Kylee Mroz</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>kybrownandfam@gmail.com</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr"/>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>168K</t>
+        </is>
+      </c>
+      <c r="F94" t="n">
+        <v>167800</v>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Family &amp; Children</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Sarasota, FL, US</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>Lifestyle</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/kyleemroz</t>
+        </is>
+      </c>
+      <c r="K94" t="b">
+        <v>1</v>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>$300</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>1 TikTok Video (60 Seconds)</t>
+        </is>
+      </c>
+      <c r="O94" t="inlineStr">
+        <is>
+          <t>https://beacons.ai/kyleemroz</t>
+        </is>
+      </c>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>not_sent</t>
+        </is>
+      </c>
+      <c r="Q94" t="inlineStr">
+        <is>
+          <t>2026-09-18T12:47:02.739991+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>kayeatsscharcuterie</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Promote with Kayley Burnett</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>kayeatsscharcuterie@gmail.com</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr"/>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>452K</t>
+        </is>
+      </c>
+      <c r="F95" t="n">
+        <v>451800</v>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Entrepreneur &amp; Business</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Sarasota, FL, US</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>Foodie Content Creator</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/kayeatsscharcuterie</t>
+        </is>
+      </c>
+      <c r="K95" t="b">
+        <v>1</v>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>$4,000</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>1 TikTok Video</t>
+        </is>
+      </c>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t>https://hoo.be/kayeatsscharcuterie</t>
+        </is>
+      </c>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>not_sent</t>
+        </is>
+      </c>
+      <c r="Q95" t="inlineStr">
+        <is>
+          <t>2026-09-18T12:46:58.407377+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>twofemmegems</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Promote with Cass And Alexa Meade</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>twofemmegems@gmail.com</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr"/>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>130K</t>
+        </is>
+      </c>
+      <c r="F96" t="n">
+        <v>129800</v>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>DIY &amp; Craft</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Stevensville, MD, US</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>DIY &amp; Lifestyle Influencers</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/twofemmegems</t>
+        </is>
+      </c>
+      <c r="K96" t="b">
+        <v>1</v>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>$800</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>1 Instagram Story</t>
+        </is>
+      </c>
+      <c r="O96" t="inlineStr">
+        <is>
+          <t>https://linktr.ee/twofemmegems</t>
+        </is>
+      </c>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>not_sent</t>
+        </is>
+      </c>
+      <c r="Q96" t="inlineStr">
+        <is>
+          <t>2026-09-18T12:46:05.488333+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>katvvkat</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Promote with Kat V</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>katvvkatt@gmail.com</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr"/>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>155K</t>
+        </is>
+      </c>
+      <c r="F97" t="n">
+        <v>154900</v>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Comedy &amp; Entertainment</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>San Antonio, TX, US</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>Entertainment And Lifestyle Content Creator</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/katvvkat</t>
+        </is>
+      </c>
+      <c r="K97" t="b">
+        <v>1</v>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>$115</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>1 TikTok Video (15 Seconds)</t>
+        </is>
+      </c>
+      <c r="O97" t="inlineStr">
+        <is>
+          <t>https://beacons.ai/katvvkat</t>
+        </is>
+      </c>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>not_sent</t>
+        </is>
+      </c>
+      <c r="Q97" t="inlineStr">
+        <is>
+          <t>2026-09-18T12:46:01.101141+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>maxtalkstech</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Promote with Max</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>maxtalkstechbiz@gmail.com</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr"/>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>398K</t>
+        </is>
+      </c>
+      <c r="F98" t="n">
+        <v>398000</v>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Doylestown, PA, US</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>Tech &amp; AI Content Creator</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/maxtalkstech</t>
+        </is>
+      </c>
+      <c r="K98" t="b">
+        <v>1</v>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>$1,200</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>4.2</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>1 TikTok Video (40 Seconds)</t>
+        </is>
+      </c>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>https://linktr.ee/maxtalkstech</t>
+        </is>
+      </c>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>not_sent</t>
+        </is>
+      </c>
+      <c r="Q98" t="inlineStr">
+        <is>
+          <t>2026-09-18T12:44:41.399151+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>cmyemima</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Promote with Cindy Maureen</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>cindymaurene@gmail.com</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr"/>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>218K</t>
+        </is>
+      </c>
+      <c r="F99" t="n">
+        <v>217800</v>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Irvine, CA, US</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>Public Figure, Beauty Queen, Model, Fashion Designer, and Content Creator</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/cmyemima</t>
+        </is>
+      </c>
+      <c r="K99" t="b">
+        <v>1</v>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>$210</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>1 Instagram Reel</t>
+        </is>
+      </c>
+      <c r="O99" t="inlineStr">
+        <is>
+          <t>https://hoo.be/cmyemima</t>
+        </is>
+      </c>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>not_sent</t>
+        </is>
+      </c>
+      <c r="Q99" t="inlineStr">
+        <is>
+          <t>2026-09-18T12:44:40.83674+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>douie</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Promote with Douie</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>thebloupinquiries@gmail.com</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr"/>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>242K</t>
+        </is>
+      </c>
+      <c r="F100" t="n">
+        <v>241600</v>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Comedy &amp; Entertainment</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Arlington, TX, US</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>Comedy Content Creator</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/douie</t>
+        </is>
+      </c>
+      <c r="K100" t="b">
+        <v>1</v>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>$600</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>1 Instagram Story</t>
+        </is>
+      </c>
+      <c r="O100" t="inlineStr">
+        <is>
+          <t>https://beacons.ai/douie</t>
+        </is>
+      </c>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>not_sent</t>
+        </is>
+      </c>
+      <c r="Q100" t="inlineStr">
+        <is>
+          <t>2026-09-18T12:43:13.209902+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>ellaequeue</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Promote with Gabby Mata</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>gabby@salovelist.com</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr"/>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>106K</t>
+        </is>
+      </c>
+      <c r="F101" t="n">
+        <v>106000</v>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Education</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>San Antonio, TX, US</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>Music, culture and history content creator</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/ellaequeue</t>
+        </is>
+      </c>
+      <c r="K101" t="b">
+        <v>1</v>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>$350</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>1 TikTok Video (60 Seconds)</t>
+        </is>
+      </c>
+      <c r="O101" t="inlineStr">
+        <is>
+          <t>https://beacons.ai/ellaequeue</t>
+        </is>
+      </c>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>not_sent</t>
+        </is>
+      </c>
+      <c r="Q101" t="inlineStr">
+        <is>
+          <t>2026-09-18T12:43:05.459242+00:00</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
